--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/KENTUCKY_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/KENTUCKY_2013.xlsx
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C134">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C144">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C453">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C515">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C815">
